--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UCOGA SEGUROS C.B. CHANTADA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UCOGA SEGUROS C.B. CHANTADA.xlsx
@@ -565,13 +565,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>23.2293</v>
+        <v>20.245</v>
       </c>
       <c r="E2" t="n">
-        <v>20.7368</v>
+        <v>18.2013</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4927</v>
+        <v>2.0437</v>
       </c>
       <c r="G2" t="n">
         <v>10.2905</v>
@@ -610,13 +610,13 @@
         <v>14.4926</v>
       </c>
       <c r="S2" t="n">
-        <v>6.4636</v>
+        <v>3.4794</v>
       </c>
       <c r="T2" t="n">
-        <v>4.9609</v>
+        <v>2.4256</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5027</v>
+        <v>1.0539</v>
       </c>
       <c r="V2" t="n">
         <v>10.1964</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>17.3393</v>
+        <v>18.4396</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.408899999999997</v>
+        <v>1.855200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>24.7479</v>
+        <v>16.5849</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.040400000000001</v>
+        <v>3.918200000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1947</v>
+        <v>6.834</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.235699999999999</v>
+        <v>-2.9156</v>
       </c>
       <c r="J3" t="n">
-        <v>22.3886</v>
+        <v>23.5353</v>
       </c>
       <c r="K3" t="n">
-        <v>20.3453</v>
+        <v>17.8871</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0428</v>
+        <v>5.648</v>
       </c>
       <c r="M3" t="n">
-        <v>-24.4293</v>
+        <v>-19.6171</v>
       </c>
       <c r="N3" t="n">
-        <v>-19.151</v>
+        <v>-11.0535</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.2785</v>
+        <v>-8.563700000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-10.5759</v>
+        <v>-5.4836</v>
       </c>
       <c r="Q3" t="n">
-        <v>-57.1877</v>
+        <v>-47.0033</v>
       </c>
       <c r="R3" t="n">
-        <v>46.612</v>
+        <v>41.5196</v>
       </c>
       <c r="S3" t="n">
-        <v>26.0216</v>
+        <v>8.702199999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>11.8298</v>
+        <v>3.5196</v>
       </c>
       <c r="U3" t="n">
-        <v>14.1915</v>
+        <v>5.182399999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9343</v>
+        <v>11.3035</v>
       </c>
       <c r="W3" t="n">
-        <v>15.5607</v>
+        <v>21.8035</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.6264</v>
+        <v>-10.5006</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>11.0604</v>
+        <v>14.1437</v>
       </c>
       <c r="E4" t="n">
-        <v>-15.8688</v>
+        <v>10.9518</v>
       </c>
       <c r="F4" t="n">
-        <v>26.929</v>
+        <v>3.1916</v>
       </c>
       <c r="G4" t="n">
-        <v>5.3941</v>
+        <v>10.1845</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6259000000000006</v>
+        <v>-7.6776</v>
       </c>
       <c r="I4" t="n">
-        <v>4.768200000000001</v>
+        <v>17.8625</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1911</v>
+        <v>23.6281</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3165</v>
+        <v>1.105100000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8745</v>
+        <v>22.5232</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2029</v>
+        <v>-13.4432</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6905999999999999</v>
+        <v>-8.783000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8937</v>
+        <v>-4.6608</v>
       </c>
       <c r="P4" t="n">
-        <v>-15.2762</v>
+        <v>11.9467</v>
       </c>
       <c r="Q4" t="n">
-        <v>-36.8195</v>
+        <v>-16.0594</v>
       </c>
       <c r="R4" t="n">
-        <v>21.5431</v>
+        <v>28.0062</v>
       </c>
       <c r="S4" t="n">
-        <v>24.4331</v>
+        <v>-0.8956000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>12.7006</v>
+        <v>0.7329</v>
       </c>
       <c r="U4" t="n">
-        <v>11.7324</v>
+        <v>-1.6281</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.4906</v>
+        <v>-7.0923</v>
       </c>
       <c r="W4" t="n">
-        <v>5.0591</v>
+        <v>2.6511</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.549799999999999</v>
+        <v>-9.743399999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>8.496500000000001</v>
+        <v>12.2374</v>
       </c>
       <c r="E5" t="n">
-        <v>7.783000000000001</v>
+        <v>11.4142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7135000000000002</v>
+        <v>0.8232999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>16.5822</v>
@@ -844,13 +844,13 @@
         <v>10.3799</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.9056</v>
+        <v>0.8353999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.2289</v>
+        <v>0.4023</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3234000000000001</v>
+        <v>0.4331</v>
       </c>
       <c r="V5" t="n">
         <v>6.1792</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. RUMSHA</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>6.7738</v>
+        <v>9.541700000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8513000000000006</v>
+        <v>-11.724</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9226</v>
+        <v>21.2661</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1275</v>
+        <v>-2.040400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.793000000000001</v>
+        <v>1.1947</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6655</v>
+        <v>-3.235699999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2157</v>
+        <v>22.3886</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.349399999999999</v>
+        <v>20.3453</v>
       </c>
       <c r="L6" t="n">
-        <v>4.565</v>
+        <v>2.0428</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3433</v>
+        <v>-24.4293</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4439999999999997</v>
+        <v>-19.151</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.899500000000001</v>
+        <v>-5.2785</v>
       </c>
       <c r="P6" t="n">
-        <v>-5.8756</v>
+        <v>-10.5759</v>
       </c>
       <c r="Q6" t="n">
-        <v>-16.8427</v>
+        <v>-57.1877</v>
       </c>
       <c r="R6" t="n">
-        <v>10.9673</v>
+        <v>46.612</v>
       </c>
       <c r="S6" t="n">
-        <v>10.6978</v>
+        <v>18.2241</v>
       </c>
       <c r="T6" t="n">
-        <v>8.8584</v>
+        <v>7.515</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8394</v>
+        <v>10.7095</v>
       </c>
       <c r="V6" t="n">
-        <v>4.0787</v>
+        <v>3.9343</v>
       </c>
       <c r="W6" t="n">
-        <v>7.619999999999999</v>
+        <v>15.5607</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.5413</v>
+        <v>-11.6264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>5.887999999999999</v>
+        <v>3.359199999999998</v>
       </c>
       <c r="E7" t="n">
-        <v>8.671199999999999</v>
+        <v>4.982800000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.783399999999999</v>
+        <v>-1.6238</v>
       </c>
       <c r="G7" t="n">
-        <v>10.1845</v>
+        <v>3.616400000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.6776</v>
+        <v>-6.1834</v>
       </c>
       <c r="I7" t="n">
-        <v>17.8625</v>
+        <v>9.799900000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>23.6281</v>
+        <v>31.4684</v>
       </c>
       <c r="K7" t="n">
-        <v>1.105100000000001</v>
+        <v>4.8867</v>
       </c>
       <c r="L7" t="n">
-        <v>22.5232</v>
+        <v>26.5816</v>
       </c>
       <c r="M7" t="n">
-        <v>-13.4432</v>
+        <v>-27.8517</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.783000000000001</v>
+        <v>-11.07</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.6608</v>
+        <v>-16.7817</v>
       </c>
       <c r="P7" t="n">
-        <v>11.9467</v>
+        <v>-0.1956999999999998</v>
       </c>
       <c r="Q7" t="n">
-        <v>-16.0594</v>
+        <v>-37.4069</v>
       </c>
       <c r="R7" t="n">
-        <v>28.0062</v>
+        <v>37.2109</v>
       </c>
       <c r="S7" t="n">
-        <v>-9.1511</v>
+        <v>2.4922</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.5481</v>
+        <v>-0.1299999999999998</v>
       </c>
       <c r="U7" t="n">
-        <v>-7.6032</v>
+        <v>2.6224</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.0923</v>
+        <v>-2.554</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6511</v>
+        <v>11.0523</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.743399999999999</v>
+        <v>-13.6063</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>G. RUMSHA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.677299999999999</v>
+        <v>2.5758</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.584999999999999</v>
+        <v>-3.9192</v>
       </c>
       <c r="F8" t="n">
-        <v>9.262500000000001</v>
+        <v>6.494999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>3.918200000000001</v>
+        <v>-2.1275</v>
       </c>
       <c r="H8" t="n">
-        <v>6.834</v>
+        <v>-3.793000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9156</v>
+        <v>1.6655</v>
       </c>
       <c r="J8" t="n">
-        <v>23.5353</v>
+        <v>1.2157</v>
       </c>
       <c r="K8" t="n">
-        <v>17.8871</v>
+        <v>-3.349399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>5.648</v>
+        <v>4.565</v>
       </c>
       <c r="M8" t="n">
-        <v>-19.6171</v>
+        <v>-3.3433</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.0535</v>
+        <v>-0.4439999999999997</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.563700000000001</v>
+        <v>-2.899500000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.4836</v>
+        <v>-5.8756</v>
       </c>
       <c r="Q8" t="n">
-        <v>-47.0033</v>
+        <v>-16.8427</v>
       </c>
       <c r="R8" t="n">
-        <v>41.5196</v>
+        <v>10.9673</v>
       </c>
       <c r="S8" t="n">
-        <v>-5.0607</v>
+        <v>6.4999</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.9202</v>
+        <v>4.0879</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.1404</v>
+        <v>2.412</v>
       </c>
       <c r="V8" t="n">
-        <v>11.3035</v>
+        <v>4.0787</v>
       </c>
       <c r="W8" t="n">
-        <v>21.8035</v>
+        <v>7.619999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.5006</v>
+        <v>-3.5413</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>A. GOMEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2.188599999999999</v>
+        <v>2.5661</v>
       </c>
       <c r="E9" t="n">
-        <v>8.0901</v>
+        <v>-3.580299999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.9017</v>
+        <v>6.1462</v>
       </c>
       <c r="G9" t="n">
-        <v>-7.1267</v>
+        <v>4.4335</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.158</v>
+        <v>0.9410999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.9688</v>
+        <v>3.4925</v>
       </c>
       <c r="J9" t="n">
-        <v>10.3003</v>
+        <v>1.7224</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8895</v>
+        <v>0.1819</v>
       </c>
       <c r="L9" t="n">
-        <v>6.4108</v>
+        <v>1.5405</v>
       </c>
       <c r="M9" t="n">
-        <v>-17.4271</v>
+        <v>2.711</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.0474</v>
+        <v>0.7594000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-10.3797</v>
+        <v>1.9518</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1545</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.2552</v>
+        <v>-5.0921</v>
       </c>
       <c r="R9" t="n">
-        <v>14.1009</v>
+        <v>3.1335</v>
       </c>
       <c r="S9" t="n">
-        <v>15.1652</v>
+        <v>0.03330000000000002</v>
       </c>
       <c r="T9" t="n">
-        <v>7.2063</v>
+        <v>-0.2106</v>
       </c>
       <c r="U9" t="n">
-        <v>7.9589</v>
+        <v>0.2439</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6957</v>
+        <v>0.0576000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>6.8392</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-10.5348</v>
+        <v>0.0576000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GOMEZ VAZQUEZ</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06419999999999992</v>
+        <v>-0.9798000000000009</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.927</v>
+        <v>0.2668999999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>4.9912</v>
+        <v>-1.2466</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4335</v>
+        <v>-4.590599999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9410999999999999</v>
+        <v>1.6184</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4925</v>
+        <v>-6.209099999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7224</v>
+        <v>7.7719</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1819</v>
+        <v>6.0846</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5405</v>
+        <v>1.6868</v>
       </c>
       <c r="M10" t="n">
-        <v>2.711</v>
+        <v>-12.3624</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7594000000000001</v>
+        <v>-4.4665</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9518</v>
+        <v>-7.896</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9585</v>
+        <v>-6.6587</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0921</v>
+        <v>-18.8013</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1335</v>
+        <v>12.1424</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4684</v>
+        <v>2.6496</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5573</v>
+        <v>-0.07589999999999997</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.911</v>
+        <v>2.7257</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0576000000000001</v>
+        <v>7.6201</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>11.3725</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0576000000000001</v>
+        <v>-3.7525</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4541</v>
+        <v>-2.2448</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4421</v>
+        <v>-2.3398</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01200000000000007</v>
+        <v>0.09489999999999993</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1514</v>
@@ -1312,13 +1312,13 @@
         <v>0.3916</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6944999999999999</v>
+        <v>-0.4852</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2786999999999999</v>
+        <v>-0.1717</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. NIETO GONZALEZ</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4507</v>
+        <v>-3.2698</v>
       </c>
       <c r="E12" t="n">
-        <v>3.671199999999998</v>
+        <v>-5.293799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.1219</v>
+        <v>2.0239</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.132299999999999</v>
+        <v>1.5311</v>
       </c>
       <c r="H12" t="n">
-        <v>5.373800000000001</v>
+        <v>4.1228</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.5063</v>
+        <v>-2.5918</v>
       </c>
       <c r="J12" t="n">
-        <v>9.8889</v>
+        <v>0.4542</v>
       </c>
       <c r="K12" t="n">
-        <v>6.8809</v>
+        <v>4.457199999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0081</v>
+        <v>-4.0029</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.0214</v>
+        <v>1.0768</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5072</v>
+        <v>-0.3344</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.5141</v>
+        <v>1.4112</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9583</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.9348</v>
+        <v>-4.3087</v>
       </c>
       <c r="R12" t="n">
-        <v>23.8932</v>
+        <v>3.9169</v>
       </c>
       <c r="S12" t="n">
-        <v>7.4661</v>
+        <v>0.297</v>
       </c>
       <c r="T12" t="n">
-        <v>11.6444</v>
+        <v>-0.05</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1784</v>
+        <v>0.347</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.742799999999999</v>
+        <v>-4.706300000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>4.0729</v>
+        <v>-1.3894</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.8157</v>
+        <v>-3.3169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.756100000000001</v>
+        <v>-3.5921</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.730600000000001</v>
+        <v>-24.6037</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.02549999999999919</v>
+        <v>21.0115</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.590599999999999</v>
+        <v>5.3941</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6184</v>
+        <v>0.6259000000000006</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.209099999999999</v>
+        <v>4.768200000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>7.7719</v>
+        <v>3.1911</v>
       </c>
       <c r="K13" t="n">
-        <v>6.0846</v>
+        <v>1.3165</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6868</v>
+        <v>1.8745</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.3624</v>
+        <v>2.2029</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.4665</v>
+        <v>-0.6905999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.896</v>
+        <v>2.8937</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.6587</v>
+        <v>-15.2762</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.8013</v>
+        <v>-36.8195</v>
       </c>
       <c r="R13" t="n">
-        <v>12.1424</v>
+        <v>21.5431</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1265000000000001</v>
+        <v>9.7806</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.073399999999999</v>
+        <v>3.9657</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9467</v>
+        <v>5.8149</v>
       </c>
       <c r="V13" t="n">
-        <v>7.6201</v>
+        <v>-3.4906</v>
       </c>
       <c r="W13" t="n">
-        <v>11.3725</v>
+        <v>5.0591</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.7525</v>
+        <v>-8.549799999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>A. VAZQUEZ ABAD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9371</v>
+        <v>-4.4013</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.5812</v>
+        <v>-3.0592</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6441</v>
+        <v>-1.342</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5311</v>
+        <v>-0.3547000000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1228</v>
+        <v>-0.3952999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.5918</v>
+        <v>0.04079999999999995</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4542</v>
+        <v>1.0423</v>
       </c>
       <c r="K14" t="n">
-        <v>4.457199999999999</v>
+        <v>0.3504</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.0029</v>
+        <v>0.6918999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0768</v>
+        <v>-1.3969</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3344</v>
+        <v>-0.7458999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4112</v>
+        <v>-0.6512</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3917</v>
+        <v>-3.5252</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.3087</v>
+        <v>-3.9169</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9169</v>
+        <v>0.3916</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3702</v>
+        <v>-0.246</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3374</v>
+        <v>-0.1847</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03290000000000004</v>
+        <v>-0.06129999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.706300000000001</v>
+        <v>-0.2754</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.3894</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.3169</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ ABAD</t>
+          <t>J. NIETO GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.324400000000001</v>
+        <v>-5.466000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.528</v>
+        <v>-1.8685</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7962</v>
+        <v>-3.597900000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3547000000000002</v>
+        <v>-5.132299999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3952999999999999</v>
+        <v>5.373800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04079999999999995</v>
+        <v>-10.5063</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0423</v>
+        <v>9.8889</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3504</v>
+        <v>6.8809</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6918999999999998</v>
+        <v>3.0081</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3969</v>
+        <v>-15.0214</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7458999999999999</v>
+        <v>-1.5072</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6512</v>
+        <v>-13.5141</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.5252</v>
+        <v>1.9583</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9169</v>
+        <v>-21.9348</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3916</v>
+        <v>23.8932</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1691</v>
+        <v>5.4503</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6534</v>
+        <v>6.1047</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5156999999999999</v>
+        <v>-0.6543000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2754</v>
+        <v>-7.742799999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>4.0729</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2754</v>
+        <v>-11.8157</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. DIAZ VALIN</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.277199999999999</v>
+        <v>-6.1059</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.6311</v>
+        <v>2.920500000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>4.354</v>
+        <v>-9.0265</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7996</v>
+        <v>-7.1267</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5155</v>
+        <v>-3.158</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2840000000000001</v>
+        <v>-3.9688</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2167</v>
+        <v>10.3003</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5823</v>
+        <v>3.8895</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3656</v>
+        <v>6.4108</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4170000000000003</v>
+        <v>-17.4271</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0667</v>
+        <v>-7.0474</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6495000000000001</v>
+        <v>-10.3797</v>
       </c>
       <c r="P16" t="n">
-        <v>-5.483700000000001</v>
+        <v>-2.1545</v>
       </c>
       <c r="Q16" t="n">
-        <v>-13.1218</v>
+        <v>-16.2552</v>
       </c>
       <c r="R16" t="n">
-        <v>7.638</v>
+        <v>14.1009</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7435</v>
+        <v>6.8708</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.6107</v>
+        <v>2.0365</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8673</v>
+        <v>4.8341</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.8496</v>
+        <v>-3.6957</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.1152</v>
+        <v>6.8392</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.7344</v>
+        <v>-10.5348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>P. DIAZ VALIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.2796</v>
+        <v>-6.107200000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.019399999999999</v>
+        <v>-10.5709</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.2605</v>
+        <v>4.4637</v>
       </c>
       <c r="G17" t="n">
-        <v>3.616400000000001</v>
+        <v>1.7996</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.1834</v>
+        <v>1.5155</v>
       </c>
       <c r="I17" t="n">
-        <v>9.799900000000001</v>
+        <v>0.2840000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>31.4684</v>
+        <v>2.2167</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8867</v>
+        <v>2.5823</v>
       </c>
       <c r="L17" t="n">
-        <v>26.5816</v>
+        <v>-0.3656</v>
       </c>
       <c r="M17" t="n">
-        <v>-27.8517</v>
+        <v>-0.4170000000000003</v>
       </c>
       <c r="N17" t="n">
-        <v>-11.07</v>
+        <v>-1.0667</v>
       </c>
       <c r="O17" t="n">
-        <v>-16.7817</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1956999999999998</v>
+        <v>-5.483700000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-37.4069</v>
+        <v>-13.1218</v>
       </c>
       <c r="R17" t="n">
-        <v>37.2109</v>
+        <v>7.638</v>
       </c>
       <c r="S17" t="n">
-        <v>-12.1465</v>
+        <v>1.4264</v>
       </c>
       <c r="T17" t="n">
-        <v>-11.1324</v>
+        <v>0.4492</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0141</v>
+        <v>0.9771000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.554</v>
+        <v>-3.8496</v>
       </c>
       <c r="W17" t="n">
-        <v>11.0523</v>
+        <v>-0.1152</v>
       </c>
       <c r="X17" t="n">
-        <v>-13.6063</v>
+        <v>-3.7344</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.3806</v>
+        <v>-18.6916</v>
       </c>
       <c r="E18" t="n">
-        <v>-16.56</v>
+        <v>-15.0056</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8207</v>
+        <v>-3.6863</v>
       </c>
       <c r="G18" t="n">
         <v>-23.7709</v>
@@ -1858,13 +1858,13 @@
         <v>19.3886</v>
       </c>
       <c r="S18" t="n">
-        <v>10.3572</v>
+        <v>11.0463</v>
       </c>
       <c r="T18" t="n">
-        <v>4.287199999999999</v>
+        <v>5.8417</v>
       </c>
       <c r="U18" t="n">
-        <v>6.0698</v>
+        <v>5.2044</v>
       </c>
       <c r="V18" t="n">
         <v>0.1047000000000002</v>
@@ -1891,13 +1891,13 @@
         <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>-41.9647</v>
+        <v>-32.6291</v>
       </c>
       <c r="E19" t="n">
-        <v>-33.5534</v>
+        <v>-25.4822</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.411499999999998</v>
+        <v>-7.146800000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-12.9525</v>
@@ -1936,13 +1936,13 @@
         <v>28.3978</v>
       </c>
       <c r="S19" t="n">
-        <v>-8.0631</v>
+        <v>1.2727</v>
       </c>
       <c r="T19" t="n">
-        <v>-8.889199999999999</v>
+        <v>-0.8180999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8261000000000001</v>
+        <v>2.091</v>
       </c>
       <c r="V19" t="n">
         <v>-6.065</v>
@@ -1969,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>-22.1071</v>
+        <v>-0.3791000000000011</v>
       </c>
       <c r="E20" t="n">
-        <v>-69.03189999999999</v>
+        <v>-56.8545</v>
       </c>
       <c r="F20" t="n">
-        <v>46.9241</v>
+        <v>56.47489999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-2.496899999999998</v>
@@ -2014,13 +2014,13 @@
         <v>324.1261</v>
       </c>
       <c r="S20" t="n">
-        <v>55.7054</v>
+        <v>77.43339999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>23.1208</v>
+        <v>35.2983</v>
       </c>
       <c r="U20" t="n">
-        <v>32.5838</v>
+        <v>42.136</v>
       </c>
       <c r="V20" t="n">
         <v>4.002799999999999</v>
